--- a/data/weeks/CTR_PS_03_06_2026-09_06_2026.xlsx
+++ b/data/weeks/CTR_PS_03_06_2026-09_06_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\E BACKUP\DATA\Web Upload\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{78E93E02-FE81-4DD3-9916-12F2AC7AAC79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{94AA4BE3-AF50-4CA6-A41F-419BA2E911E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{DB0A502A-9216-4457-A864-741E272692D3}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D5AFBC0A-0FFD-44EC-9E81-CA5F7E0D3682}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -646,7 +646,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73C27326-3CF4-44A1-B048-6933FE0297BB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C03B5CF-D3F6-4D59-BFD8-DB166D011243}">
   <sheetPr codeName="Sheet37">
     <tabColor rgb="FF00B0F0"/>
     <pageSetUpPr fitToPage="1"/>
@@ -869,7 +869,7 @@
         <v>50</v>
       </c>
       <c r="T3" s="10">
-        <v>93.993677555321383</v>
+        <v>100</v>
       </c>
       <c r="U3" s="10">
         <v>100</v>
@@ -937,7 +937,7 @@
         <v>46</v>
       </c>
       <c r="T4" s="10">
-        <v>88.883034773445729</v>
+        <v>100</v>
       </c>
       <c r="U4" s="10">
         <v>90</v>
@@ -1005,7 +1005,7 @@
         <v>50</v>
       </c>
       <c r="T5" s="10">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="U5" s="10">
         <v>100</v>
@@ -1073,7 +1073,7 @@
         <v>50</v>
       </c>
       <c r="T6" s="10">
-        <v>97.365648050579551</v>
+        <v>100</v>
       </c>
       <c r="U6" s="10">
         <v>100</v>
@@ -1141,7 +1141,7 @@
         <v>96</v>
       </c>
       <c r="T7" s="10">
-        <v>97.787144362486828</v>
+        <v>80</v>
       </c>
       <c r="U7" s="10">
         <v>100</v>
@@ -1209,7 +1209,7 @@
         <v>97</v>
       </c>
       <c r="T8" s="10">
-        <v>80.927291886195988</v>
+        <v>100</v>
       </c>
       <c r="U8" s="10">
         <v>40</v>
@@ -1277,7 +1277,7 @@
         <v>50</v>
       </c>
       <c r="T9" s="10">
-        <v>92.518440463645945</v>
+        <v>100</v>
       </c>
       <c r="U9" s="10">
         <v>100</v>
@@ -1345,7 +1345,7 @@
         <v>97</v>
       </c>
       <c r="T10" s="10">
-        <v>94.783983140147527</v>
+        <v>100</v>
       </c>
       <c r="U10" s="10">
         <v>80</v>
@@ -1413,7 +1413,7 @@
         <v>89</v>
       </c>
       <c r="T11" s="10">
-        <v>83.19283456269757</v>
+        <v>100</v>
       </c>
       <c r="U11" s="10">
         <v>100</v>
@@ -1481,7 +1481,7 @@
         <v>50</v>
       </c>
       <c r="T12" s="10">
-        <v>83.403582718651208</v>
+        <v>100</v>
       </c>
       <c r="U12" s="10">
         <v>40</v>
@@ -1549,7 +1549,7 @@
         <v>50</v>
       </c>
       <c r="T13" s="10">
-        <v>89.462592202318234</v>
+        <v>67</v>
       </c>
       <c r="U13" s="10">
         <v>100</v>
@@ -1685,7 +1685,7 @@
         <v>37</v>
       </c>
       <c r="T15" s="10">
-        <v>90.147523709167544</v>
+        <v>100</v>
       </c>
       <c r="U15" s="10">
         <v>60</v>
@@ -1753,7 +1753,7 @@
         <v>50</v>
       </c>
       <c r="T16" s="10">
-        <v>84.299262381454156</v>
+        <v>100</v>
       </c>
       <c r="U16" s="10">
         <v>100</v>
@@ -1821,7 +1821,7 @@
         <v>50</v>
       </c>
       <c r="T17" s="10">
-        <v>79.34668071654373</v>
+        <v>100</v>
       </c>
       <c r="U17" s="10">
         <v>80</v>
@@ -1889,7 +1889,7 @@
         <v>96</v>
       </c>
       <c r="T18" s="10">
-        <v>90.147523709167544</v>
+        <v>100</v>
       </c>
       <c r="U18" s="10">
         <v>100</v>
@@ -2025,7 +2025,7 @@
         <v>95</v>
       </c>
       <c r="T20" s="10">
-        <v>87.618545837723914</v>
+        <v>100</v>
       </c>
       <c r="U20" s="10">
         <v>90</v>
@@ -2093,7 +2093,7 @@
         <v>50</v>
       </c>
       <c r="T21" s="10">
-        <v>94.520547945205479</v>
+        <v>100</v>
       </c>
       <c r="U21" s="10">
         <v>100</v>
@@ -2161,7 +2161,7 @@
         <v>96</v>
       </c>
       <c r="T22" s="10">
-        <v>74.657534246575352</v>
+        <v>100</v>
       </c>
       <c r="U22" s="10">
         <v>100</v>
@@ -2229,7 +2229,7 @@
         <v>81</v>
       </c>
       <c r="T23" s="10">
-        <v>84.141201264488927</v>
+        <v>100</v>
       </c>
       <c r="U23" s="10">
         <v>100</v>
@@ -2297,7 +2297,7 @@
         <v>89</v>
       </c>
       <c r="T24" s="10">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="U24" s="10">
         <v>100</v>
@@ -2365,7 +2365,7 @@
         <v>50</v>
       </c>
       <c r="T25" s="10">
-        <v>80.769230769230774</v>
+        <v>100</v>
       </c>
       <c r="U25" s="10">
         <v>100</v>
@@ -2433,7 +2433,7 @@
         <v>50</v>
       </c>
       <c r="T26" s="10">
-        <v>91.88619599578503</v>
+        <v>100</v>
       </c>
       <c r="U26" s="10">
         <v>100</v>
@@ -2501,7 +2501,7 @@
         <v>50</v>
       </c>
       <c r="T27" s="10">
-        <v>89.567966280295039</v>
+        <v>100</v>
       </c>
       <c r="U27" s="10">
         <v>100</v>
@@ -2569,7 +2569,7 @@
         <v>100</v>
       </c>
       <c r="T28" s="10">
-        <v>85.458377239199152</v>
+        <v>100</v>
       </c>
       <c r="U28" s="10">
         <v>100</v>
@@ -2637,7 +2637,7 @@
         <v>50</v>
       </c>
       <c r="T29" s="10">
-        <v>93.572181243414121</v>
+        <v>100</v>
       </c>
       <c r="U29" s="10">
         <v>100</v>
@@ -2705,7 +2705,7 @@
         <v>50</v>
       </c>
       <c r="T30" s="10">
-        <v>96.944151738672289</v>
+        <v>100</v>
       </c>
       <c r="U30" s="10">
         <v>90</v>
@@ -2773,7 +2773,7 @@
         <v>69</v>
       </c>
       <c r="T31" s="10">
-        <v>88.408851422550043</v>
+        <v>100</v>
       </c>
       <c r="U31" s="10">
         <v>100</v>
@@ -2841,7 +2841,7 @@
         <v>50</v>
       </c>
       <c r="T32" s="10">
-        <v>85.142255005268694</v>
+        <v>100</v>
       </c>
       <c r="U32" s="10">
         <v>100</v>
@@ -2909,7 +2909,7 @@
         <v>94</v>
       </c>
       <c r="T33" s="10">
-        <v>67.755532139093788</v>
+        <v>100</v>
       </c>
       <c r="U33" s="10">
         <v>100</v>
@@ -2977,7 +2977,7 @@
         <v>75</v>
       </c>
       <c r="T34" s="10">
-        <v>87.776606954689157</v>
+        <v>100</v>
       </c>
       <c r="U34" s="10">
         <v>100</v>
@@ -3045,7 +3045,7 @@
         <v>50</v>
       </c>
       <c r="T35" s="10">
-        <v>66.174920969441501</v>
+        <v>100</v>
       </c>
       <c r="U35" s="10">
         <v>100</v>
@@ -3113,7 +3113,7 @@
         <v>50</v>
       </c>
       <c r="T36" s="10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U36" s="10">
         <v>10</v>

--- a/data/weeks/CTR_PS_03_06_2026-09_06_2026.xlsx
+++ b/data/weeks/CTR_PS_03_06_2026-09_06_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\E BACKUP\DATA\Web Upload\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{94AA4BE3-AF50-4CA6-A41F-419BA2E911E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E5BF5366-D9C4-4E03-9D63-254728458C86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D5AFBC0A-0FFD-44EC-9E81-CA5F7E0D3682}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6075A4C5-56E8-497E-9AE1-468447C7D954}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -646,7 +646,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C03B5CF-D3F6-4D59-BFD8-DB166D011243}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79EFA808-5C14-4A01-A328-24B1CFC04F0B}">
   <sheetPr codeName="Sheet37">
     <tabColor rgb="FF00B0F0"/>
     <pageSetUpPr fitToPage="1"/>
@@ -866,10 +866,10 @@
         <v>50</v>
       </c>
       <c r="S3" s="10">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T3" s="10">
-        <v>100</v>
+        <v>93.993677555321383</v>
       </c>
       <c r="U3" s="10">
         <v>100</v>
@@ -934,10 +934,10 @@
         <v>46</v>
       </c>
       <c r="S4" s="10">
-        <v>46</v>
+        <v>100</v>
       </c>
       <c r="T4" s="10">
-        <v>100</v>
+        <v>88.883034773445729</v>
       </c>
       <c r="U4" s="10">
         <v>90</v>
@@ -1002,10 +1002,10 @@
         <v>50</v>
       </c>
       <c r="S5" s="10">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T5" s="10">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="U5" s="10">
         <v>100</v>
@@ -1070,10 +1070,10 @@
         <v>50</v>
       </c>
       <c r="S6" s="10">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T6" s="10">
-        <v>100</v>
+        <v>97.365648050579551</v>
       </c>
       <c r="U6" s="10">
         <v>100</v>
@@ -1138,10 +1138,10 @@
         <v>96</v>
       </c>
       <c r="S7" s="10">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="T7" s="10">
-        <v>80</v>
+        <v>97.787144362486828</v>
       </c>
       <c r="U7" s="10">
         <v>100</v>
@@ -1206,10 +1206,10 @@
         <v>97</v>
       </c>
       <c r="S8" s="10">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="T8" s="10">
-        <v>100</v>
+        <v>80.927291886195988</v>
       </c>
       <c r="U8" s="10">
         <v>40</v>
@@ -1274,10 +1274,10 @@
         <v>50</v>
       </c>
       <c r="S9" s="10">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T9" s="10">
-        <v>100</v>
+        <v>92.518440463645945</v>
       </c>
       <c r="U9" s="10">
         <v>100</v>
@@ -1342,10 +1342,10 @@
         <v>97</v>
       </c>
       <c r="S10" s="10">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="T10" s="10">
-        <v>100</v>
+        <v>94.783983140147527</v>
       </c>
       <c r="U10" s="10">
         <v>80</v>
@@ -1410,10 +1410,10 @@
         <v>89</v>
       </c>
       <c r="S11" s="10">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="T11" s="10">
-        <v>100</v>
+        <v>83.19283456269757</v>
       </c>
       <c r="U11" s="10">
         <v>100</v>
@@ -1478,10 +1478,10 @@
         <v>50</v>
       </c>
       <c r="S12" s="10">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T12" s="10">
-        <v>100</v>
+        <v>83.403582718651208</v>
       </c>
       <c r="U12" s="10">
         <v>40</v>
@@ -1546,10 +1546,10 @@
         <v>50</v>
       </c>
       <c r="S13" s="10">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="T13" s="10">
-        <v>67</v>
+        <v>89.462592202318234</v>
       </c>
       <c r="U13" s="10">
         <v>100</v>
@@ -1614,7 +1614,7 @@
         <v>50</v>
       </c>
       <c r="S14" s="10">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T14" s="10">
         <v>100</v>
@@ -1682,10 +1682,10 @@
         <v>37</v>
       </c>
       <c r="S15" s="10">
-        <v>37</v>
+        <v>100</v>
       </c>
       <c r="T15" s="10">
-        <v>100</v>
+        <v>90.147523709167544</v>
       </c>
       <c r="U15" s="10">
         <v>60</v>
@@ -1750,10 +1750,10 @@
         <v>50</v>
       </c>
       <c r="S16" s="10">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T16" s="10">
-        <v>100</v>
+        <v>84.299262381454156</v>
       </c>
       <c r="U16" s="10">
         <v>100</v>
@@ -1818,10 +1818,10 @@
         <v>50</v>
       </c>
       <c r="S17" s="10">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T17" s="10">
-        <v>100</v>
+        <v>79.34668071654373</v>
       </c>
       <c r="U17" s="10">
         <v>80</v>
@@ -1886,10 +1886,10 @@
         <v>96</v>
       </c>
       <c r="S18" s="10">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="T18" s="10">
-        <v>100</v>
+        <v>90.147523709167544</v>
       </c>
       <c r="U18" s="10">
         <v>100</v>
@@ -2022,10 +2022,10 @@
         <v>95</v>
       </c>
       <c r="S20" s="10">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="T20" s="10">
-        <v>100</v>
+        <v>87.618545837723914</v>
       </c>
       <c r="U20" s="10">
         <v>90</v>
@@ -2090,10 +2090,10 @@
         <v>50</v>
       </c>
       <c r="S21" s="10">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T21" s="10">
-        <v>100</v>
+        <v>94.520547945205479</v>
       </c>
       <c r="U21" s="10">
         <v>100</v>
@@ -2158,10 +2158,10 @@
         <v>96</v>
       </c>
       <c r="S22" s="10">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="T22" s="10">
-        <v>100</v>
+        <v>74.657534246575352</v>
       </c>
       <c r="U22" s="10">
         <v>100</v>
@@ -2226,10 +2226,10 @@
         <v>81</v>
       </c>
       <c r="S23" s="10">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="T23" s="10">
-        <v>100</v>
+        <v>84.141201264488927</v>
       </c>
       <c r="U23" s="10">
         <v>100</v>
@@ -2294,10 +2294,10 @@
         <v>89</v>
       </c>
       <c r="S24" s="10">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="T24" s="10">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="U24" s="10">
         <v>100</v>
@@ -2362,10 +2362,10 @@
         <v>50</v>
       </c>
       <c r="S25" s="10">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T25" s="10">
-        <v>100</v>
+        <v>80.769230769230774</v>
       </c>
       <c r="U25" s="10">
         <v>100</v>
@@ -2430,10 +2430,10 @@
         <v>50</v>
       </c>
       <c r="S26" s="10">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T26" s="10">
-        <v>100</v>
+        <v>91.88619599578503</v>
       </c>
       <c r="U26" s="10">
         <v>100</v>
@@ -2498,10 +2498,10 @@
         <v>50</v>
       </c>
       <c r="S27" s="10">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T27" s="10">
-        <v>100</v>
+        <v>89.567966280295039</v>
       </c>
       <c r="U27" s="10">
         <v>100</v>
@@ -2569,7 +2569,7 @@
         <v>100</v>
       </c>
       <c r="T28" s="10">
-        <v>100</v>
+        <v>85.458377239199152</v>
       </c>
       <c r="U28" s="10">
         <v>100</v>
@@ -2634,10 +2634,10 @@
         <v>50</v>
       </c>
       <c r="S29" s="10">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T29" s="10">
-        <v>100</v>
+        <v>93.572181243414121</v>
       </c>
       <c r="U29" s="10">
         <v>100</v>
@@ -2702,10 +2702,10 @@
         <v>50</v>
       </c>
       <c r="S30" s="10">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T30" s="10">
-        <v>100</v>
+        <v>96.944151738672289</v>
       </c>
       <c r="U30" s="10">
         <v>90</v>
@@ -2770,10 +2770,10 @@
         <v>69</v>
       </c>
       <c r="S31" s="10">
-        <v>69</v>
+        <v>100</v>
       </c>
       <c r="T31" s="10">
-        <v>100</v>
+        <v>88.408851422550043</v>
       </c>
       <c r="U31" s="10">
         <v>100</v>
@@ -2838,10 +2838,10 @@
         <v>50</v>
       </c>
       <c r="S32" s="10">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T32" s="10">
-        <v>100</v>
+        <v>85.142255005268694</v>
       </c>
       <c r="U32" s="10">
         <v>100</v>
@@ -2906,10 +2906,10 @@
         <v>94</v>
       </c>
       <c r="S33" s="10">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="T33" s="10">
-        <v>100</v>
+        <v>67.755532139093788</v>
       </c>
       <c r="U33" s="10">
         <v>100</v>
@@ -2974,10 +2974,10 @@
         <v>75</v>
       </c>
       <c r="S34" s="10">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="T34" s="10">
-        <v>100</v>
+        <v>87.776606954689157</v>
       </c>
       <c r="U34" s="10">
         <v>100</v>
@@ -3042,10 +3042,10 @@
         <v>50</v>
       </c>
       <c r="S35" s="10">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T35" s="10">
-        <v>100</v>
+        <v>66.174920969441501</v>
       </c>
       <c r="U35" s="10">
         <v>100</v>
@@ -3110,10 +3110,10 @@
         <v>50</v>
       </c>
       <c r="S36" s="10">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T36" s="10">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U36" s="10">
         <v>10</v>
